--- a/src/test/resources/Datasheet.xlsx
+++ b/src/test/resources/Datasheet.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="test2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -16,25 +16,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>a</t>
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>FieldName</t>
+  </si>
+  <si>
+    <t>xpathValue</t>
+  </si>
+  <si>
+    <t>dataValue</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>//input[@name='firstName'</t>
+  </si>
+  <si>
+    <t>testA</t>
+  </si>
+  <si>
+    <t>//input[@name='lastName'</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>showPassword</t>
+  </si>
+  <si>
+    <t>//input[@type='checkbox'</t>
+  </si>
+  <si>
+    <t>testB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,8 +96,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -395,10 +438,58 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
